--- a/010_Can_SapCoupa_Doordash_Dispatcher/Data/CanSapAribaDoordashDispatcherConfig.xlsx
+++ b/010_Can_SapCoupa_Doordash_Dispatcher/Data/CanSapAribaDoordashDispatcherConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://insidemedia-my.sharepoint.com/personal/forms_membership__nycgrm_ar_service_groupm_com/Documents/Desktop/Aniket Code/010_Can_SapCoupa_Doordash/010_Can_SapCoupa_Doordash_Dispatcher/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{B464C772-0EF5-4002-9488-2DA611DCFF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41777BCA-9635-48D2-88AC-92BE8E86053B}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{B464C772-0EF5-4002-9488-2DA611DCFF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3D87BA-5A67-4CA1-A395-178CA87A2D4C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="10170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -264,9 +264,6 @@
     <t>&lt;table style='border-collapse: collapse;border: solid windowtext 1.0pt;table-layout: Auto;width: 100%;color:black;margin: 0in 0in 0.0001pt; font-size: 11pt; font-family: Calibri, sans-serif; color: #000000; font-variant-ligatures: normal; font-variant-caps: normal; font-weight: 400; letter-spacing: normal; orphans: 2; text-align: start; text-indent: 0px; text-transform: none; white-space: normal; widows: 2; word-spacing: 0px; -webkit-text-stroke-width: 0px; text-decoration-style: initial; text-decoration-color: initial;'&gt;</t>
   </si>
   <si>
-    <t>aniketni@cybage.com</t>
-  </si>
-  <si>
     <t>C:\1files\uipath\can_ar_ariba\doordash\attachments\</t>
   </si>
   <si>
@@ -286,13 +283,16 @@
   </si>
   <si>
     <t>CanSapCoupaDoordash_Queue</t>
+  </si>
+  <si>
+    <t>aniketni@cybage.com;rohitpaw@cybage.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -322,12 +322,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -346,11 +340,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -361,10 +354,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -729,7 +720,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -785,7 +776,7 @@
         <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -793,7 +784,7 @@
         <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
@@ -801,10 +792,10 @@
         <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
@@ -812,15 +803,15 @@
         <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>79</v>
+      <c r="B16" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1"/>
@@ -1830,11 +1821,8 @@
     <row r="996" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <hyperlinks>
-    <hyperlink ref="B16" r:id="rId1" xr:uid="{ACB2BA46-96D6-40BC-8794-BAFEED114C41}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3051,7 +3039,7 @@
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
         <v>58</v>
@@ -3065,7 +3053,7 @@
         <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -3079,7 +3067,7 @@
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -3093,7 +3081,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -3107,7 +3095,7 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
         <v>62</v>
@@ -3121,7 +3109,7 @@
         <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
         <v>63</v>
@@ -4361,15 +4349,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
@@ -4379,6 +4358,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4401,14 +4389,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1451EC1E-2FC7-45C1-A096-CF2F1D99CEA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{267B89B1-EC80-4460-B457-5C0CB7C26FA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4417,4 +4397,12 @@
     <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1451EC1E-2FC7-45C1-A096-CF2F1D99CEA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/010_Can_SapCoupa_Doordash_Dispatcher/Data/CanSapAribaDoordashDispatcherConfig.xlsx
+++ b/010_Can_SapCoupa_Doordash_Dispatcher/Data/CanSapAribaDoordashDispatcherConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://insidemedia-my.sharepoint.com/personal/forms_membership__nycgrm_ar_service_groupm_com/Documents/Desktop/Aniket Code/010_Can_SapCoupa_Doordash/010_Can_SapCoupa_Doordash_Dispatcher/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{B464C772-0EF5-4002-9488-2DA611DCFF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3D87BA-5A67-4CA1-A395-178CA87A2D4C}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{B464C772-0EF5-4002-9488-2DA611DCFF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41777BCA-9635-48D2-88AC-92BE8E86053B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="10170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -264,6 +264,9 @@
     <t>&lt;table style='border-collapse: collapse;border: solid windowtext 1.0pt;table-layout: Auto;width: 100%;color:black;margin: 0in 0in 0.0001pt; font-size: 11pt; font-family: Calibri, sans-serif; color: #000000; font-variant-ligatures: normal; font-variant-caps: normal; font-weight: 400; letter-spacing: normal; orphans: 2; text-align: start; text-indent: 0px; text-transform: none; white-space: normal; widows: 2; word-spacing: 0px; -webkit-text-stroke-width: 0px; text-decoration-style: initial; text-decoration-color: initial;'&gt;</t>
   </si>
   <si>
+    <t>aniketni@cybage.com</t>
+  </si>
+  <si>
     <t>C:\1files\uipath\can_ar_ariba\doordash\attachments\</t>
   </si>
   <si>
@@ -283,16 +286,13 @@
   </si>
   <si>
     <t>CanSapCoupaDoordash_Queue</t>
-  </si>
-  <si>
-    <t>aniketni@cybage.com;rohitpaw@cybage.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -322,6 +322,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -340,10 +346,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -354,8 +361,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -720,7 +729,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -776,7 +785,7 @@
         <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -784,7 +793,7 @@
         <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
@@ -792,10 +801,10 @@
         <v>67</v>
       </c>
       <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
         <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
@@ -803,15 +812,15 @@
         <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
         <v>69</v>
       </c>
-      <c r="B16" t="s">
-        <v>86</v>
+      <c r="B16" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1"/>
@@ -1821,8 +1830,11 @@
     <row r="996" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="B16" r:id="rId1" xr:uid="{ACB2BA46-96D6-40BC-8794-BAFEED114C41}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3039,7 +3051,7 @@
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
         <v>58</v>
@@ -3053,7 +3065,7 @@
         <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -3067,7 +3079,7 @@
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -3081,7 +3093,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -3095,7 +3107,7 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
         <v>62</v>
@@ -3109,7 +3121,7 @@
         <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
         <v>63</v>
@@ -4349,6 +4361,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
@@ -4358,15 +4379,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4389,6 +4401,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1451EC1E-2FC7-45C1-A096-CF2F1D99CEA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{267B89B1-EC80-4460-B457-5C0CB7C26FA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4397,12 +4417,4 @@
     <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1451EC1E-2FC7-45C1-A096-CF2F1D99CEA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>